--- a/Тест2/274.xlsx
+++ b/Тест2/274.xlsx
@@ -126,16 +126,16 @@
     <t xml:space="preserve">Kolbasa namunasi olishda nimalar tekshiriladi?</t>
   </si>
   <si>
-    <t xml:space="preserve">Idish hajmi, vazni va shakli</t>
+    <t xml:space="preserve">Idish hajmi, vazni va shakli haqida</t>
   </si>
   <si>
     <t xml:space="preserve">Sotuvchi ismi, manzili va telefoni</t>
   </si>
   <si>
-    <t xml:space="preserve">O'rami rangi, narxi va dizayni</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reklama matni va shtrix-kodi</t>
+    <t xml:space="preserve">O'rami rangi, narxi va dizayni haqida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reklama matni va shtrix-kod rangi</t>
   </si>
   <si>
     <t xml:space="preserve">O'ramning butunligi, sana va partiya raqami</t>
@@ -210,19 +210,19 @@
     <t xml:space="preserve">Muzlatilgan namunalar nega maxsus tartibda tekshiriladi?</t>
   </si>
   <si>
-    <t xml:space="preserve">Muzlatish mikroblarni sterillaydi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Muzlatish mikroblarni ko'paytiradi</t>
+    <t xml:space="preserve">Muzlatish barcha mikroblarni sterillaydi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muzlatish barcha mikroblarni ko'paytiradi</t>
   </si>
   <si>
     <t xml:space="preserve">Muzlatish ba'zi mikroblarga zarar yetkazadi</t>
   </si>
   <si>
-    <t xml:space="preserve">Muzlatish hajmini kamaytiradi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Muzlatish rangini o'zgartiradi</t>
+    <t xml:space="preserve">Muzlatish namuna hajmini kamaytiradi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Muzlatish namuna rangini o'zgartiradi</t>
   </si>
   <si>
     <t xml:space="preserve">To'g'ri javob: Muzlatish ba'zi mikroblarga zarar yetkazadi. Muzlatish ba'zi mikroblarga zarar yetkazishi mumkin, shuning uchun muzlatilgan namunalar maxsus tartibda tekshiriladi. Manba: Mavzu materiali (274.docx).</t>
